--- a/RAMON FRANCO/Junio/CALCULO EDESUR RAMON FRANCO Abirl.xlsx
+++ b/RAMON FRANCO/Junio/CALCULO EDESUR RAMON FRANCO Abirl.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2AD2E1-6C20-4DAF-AF78-5210BD0624A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F21C62B-D61C-4E0D-904D-B24E9DA94084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,7 +339,7 @@
     <t>QUIENES ADEUDEN DOS MESES DE EDESUR SERAN DESCONECTADOS DE LA RED. SALUDOS CORDIALES.</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 16/06</t>
+    <t>EDESUR - VENCIMIENTO 14/07</t>
   </si>
 </sst>
 </file>
@@ -355,7 +355,7 @@
     <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +442,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -904,16 +911,6 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -937,9 +934,19 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1265,22 +1272,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="91"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="107"/>
       <c r="O1" s="48"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
@@ -1433,8 +1440,8 @@
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="87">
-        <v>748259.39</v>
+      <c r="C8" s="110">
+        <v>631229.38</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1444,7 +1451,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="47">
         <f>C8-J32</f>
-        <v>457301.16629000014</v>
+        <v>340271.15629000013</v>
       </c>
       <c r="L8" s="47"/>
       <c r="M8" s="10"/>
@@ -1503,96 +1510,96 @@
       <c r="A10" s="71">
         <v>1</v>
       </c>
-      <c r="B10" s="93">
+      <c r="B10" s="87">
         <v>1</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="96">
+      <c r="E10" s="90">
         <v>7.99</v>
       </c>
-      <c r="F10" s="97">
+      <c r="F10" s="91">
         <v>5305</v>
       </c>
-      <c r="G10" s="98">
+      <c r="G10" s="92">
         <f>+F10</f>
         <v>5305</v>
       </c>
-      <c r="H10" s="99">
-        <v>0</v>
-      </c>
-      <c r="I10" s="100">
+      <c r="H10" s="93">
+        <v>0</v>
+      </c>
+      <c r="I10" s="94">
         <f t="shared" ref="I10:I32" si="0">H10*7%</f>
         <v>0</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="95">
         <f>M10*93.787</f>
         <v>0</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="96">
         <f>K8*E10%</f>
-        <v>36538.363186571012</v>
-      </c>
-      <c r="L10" s="102"/>
-      <c r="M10" s="103">
+        <v>27187.665387571011</v>
+      </c>
+      <c r="L10" s="96"/>
+      <c r="M10" s="97">
         <f>G10-F10</f>
         <v>0</v>
       </c>
-      <c r="N10" s="104">
+      <c r="N10" s="98">
         <f>J10+K10+L10</f>
-        <v>36538.363186571012</v>
+        <v>27187.665387571011</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="71">
         <v>2</v>
       </c>
-      <c r="B11" s="105">
+      <c r="B11" s="99">
         <v>2</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="96">
+      <c r="E11" s="90">
         <v>6.05</v>
       </c>
-      <c r="F11" s="107">
+      <c r="F11" s="101">
         <v>6543</v>
       </c>
-      <c r="G11" s="98">
+      <c r="G11" s="92">
         <f>F11+200</f>
         <v>6743</v>
       </c>
-      <c r="H11" s="99">
-        <v>0</v>
-      </c>
-      <c r="I11" s="100">
+      <c r="H11" s="93">
+        <v>0</v>
+      </c>
+      <c r="I11" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="101">
+      <c r="J11" s="95">
         <f t="shared" ref="J11:J27" si="1">M11*93.787</f>
         <v>18757.400000000001</v>
       </c>
-      <c r="K11" s="102">
+      <c r="K11" s="96">
         <f>K8*E11%</f>
-        <v>27666.720560545007</v>
-      </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="103">
+        <v>20586.404955545007</v>
+      </c>
+      <c r="L11" s="96"/>
+      <c r="M11" s="97">
         <f t="shared" ref="M11:M31" si="2">G11-F11</f>
         <v>200</v>
       </c>
-      <c r="N11" s="104">
+      <c r="N11" s="98">
         <f t="shared" ref="N11:N31" si="3">J11+K11+L11</f>
-        <v>46424.120560545009</v>
+        <v>39343.804955545012</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1630,7 +1637,7 @@
       </c>
       <c r="K12" s="67">
         <f>K8*E12%</f>
-        <v>27529.530210658006</v>
+        <v>20484.323608658007</v>
       </c>
       <c r="L12" s="67"/>
       <c r="M12" s="68">
@@ -1639,7 +1646,7 @@
       </c>
       <c r="N12" s="84">
         <f t="shared" si="3"/>
-        <v>40734.739810658022</v>
+        <v>33689.533208658024</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1678,7 +1685,7 @@
       </c>
       <c r="K13" s="79">
         <f>K8*E13%</f>
-        <v>34892.078987927009</v>
+        <v>25962.689224927006</v>
       </c>
       <c r="L13" s="67"/>
       <c r="M13" s="80">
@@ -1687,7 +1694,7 @@
       </c>
       <c r="N13" s="84">
         <f t="shared" si="3"/>
-        <v>58338.828987927009</v>
+        <v>49409.439224927002</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -1726,7 +1733,7 @@
       </c>
       <c r="K14" s="57">
         <f>K8*E14%</f>
-        <v>27666.720560545007</v>
+        <v>20586.404955545007</v>
       </c>
       <c r="L14" s="57"/>
       <c r="M14" s="58">
@@ -1735,7 +1742,7 @@
       </c>
       <c r="N14" s="83">
         <f>J14+K14+L14</f>
-        <v>51113.470560545007</v>
+        <v>44033.154955545004</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -1773,7 +1780,7 @@
       </c>
       <c r="K15" s="67">
         <f>K8*E15%</f>
-        <v>27529.530210658006</v>
+        <v>20484.323608658007</v>
       </c>
       <c r="L15" s="67"/>
       <c r="M15" s="68">
@@ -1782,7 +1789,7 @@
       </c>
       <c r="N15" s="84">
         <f t="shared" si="3"/>
-        <v>55609.358010658063</v>
+        <v>48564.151408658057</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -1820,7 +1827,7 @@
       </c>
       <c r="K16" s="67">
         <f>K8*E16%</f>
-        <v>34892.078987927009</v>
+        <v>25962.689224927006</v>
       </c>
       <c r="L16" s="67"/>
       <c r="M16" s="68">
@@ -1829,7 +1836,7 @@
       </c>
       <c r="N16" s="84">
         <f t="shared" si="3"/>
-        <v>68824.215587926941</v>
+        <v>59894.825824926942</v>
       </c>
       <c r="P16" s="50"/>
     </row>
@@ -1868,7 +1875,7 @@
       </c>
       <c r="K17" s="67">
         <f>K8*E17%</f>
-        <v>27666.720560545007</v>
+        <v>20586.404955545007</v>
       </c>
       <c r="L17" s="67"/>
       <c r="M17" s="68">
@@ -1877,7 +1884,7 @@
       </c>
       <c r="N17" s="84">
         <f t="shared" si="3"/>
-        <v>53170.219470545038</v>
+        <v>46089.903865545035</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1915,7 +1922,7 @@
       </c>
       <c r="K18" s="67">
         <f>K8*E18%</f>
-        <v>27529.530210658006</v>
+        <v>20484.323608658007</v>
       </c>
       <c r="L18" s="67"/>
       <c r="M18" s="68">
@@ -1924,7 +1931,7 @@
       </c>
       <c r="N18" s="84">
         <f t="shared" si="3"/>
-        <v>42113.408710658005</v>
+        <v>35068.202108658006</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1962,7 +1969,7 @@
       </c>
       <c r="K19" s="67">
         <f>K8*E19%</f>
-        <v>96947.847253480024</v>
+        <v>72137.485133480019</v>
       </c>
       <c r="L19" s="67"/>
       <c r="M19" s="68">
@@ -1971,7 +1978,7 @@
       </c>
       <c r="N19" s="84">
         <f t="shared" si="3"/>
-        <v>119848.75691347971</v>
+        <v>95038.394793479703</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2010,7 +2017,7 @@
       </c>
       <c r="K20" s="67">
         <f>K8*E20%</f>
-        <v>31142.209424349006</v>
+        <v>23172.465743349007</v>
       </c>
       <c r="L20" s="67"/>
       <c r="M20" s="68">
@@ -2019,7 +2026,7 @@
       </c>
       <c r="N20" s="84">
         <f t="shared" si="3"/>
-        <v>76159.969424349008</v>
+        <v>68190.225743349001</v>
       </c>
       <c r="P20" s="33"/>
     </row>
@@ -2058,7 +2065,7 @@
       </c>
       <c r="K21" s="67">
         <f>K8*E21%</f>
-        <v>29816.036042108008</v>
+        <v>22185.679390108005</v>
       </c>
       <c r="L21" s="67"/>
       <c r="M21" s="68">
@@ -2067,101 +2074,101 @@
       </c>
       <c r="N21" s="84">
         <f t="shared" si="3"/>
-        <v>71900.138682108125</v>
+        <v>64269.782030108123</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>14</v>
       </c>
-      <c r="B22" s="105">
+      <c r="B22" s="99">
         <v>14</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="96">
+      <c r="E22" s="90">
         <v>1.18</v>
       </c>
-      <c r="F22" s="107">
-        <v>0</v>
-      </c>
-      <c r="G22" s="107">
-        <v>0</v>
-      </c>
-      <c r="H22" s="99">
-        <v>0</v>
-      </c>
-      <c r="I22" s="100">
+      <c r="F22" s="101">
+        <v>0</v>
+      </c>
+      <c r="G22" s="101">
+        <v>0</v>
+      </c>
+      <c r="H22" s="93">
+        <v>0</v>
+      </c>
+      <c r="I22" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="102">
+      <c r="K22" s="96">
         <f>K8*E22%</f>
-        <v>5396.1537622220012</v>
-      </c>
-      <c r="L22" s="102"/>
-      <c r="M22" s="103">
+        <v>4015.1996442220016</v>
+      </c>
+      <c r="L22" s="96"/>
+      <c r="M22" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N22" s="104">
+      <c r="N22" s="98">
         <f t="shared" si="3"/>
-        <v>5396.1537622220012</v>
+        <v>4015.1996442220016</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>15</v>
       </c>
-      <c r="B23" s="105">
+      <c r="B23" s="99">
         <v>15</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="96">
+      <c r="E23" s="90">
         <v>1.17</v>
       </c>
-      <c r="F23" s="107">
-        <v>0</v>
-      </c>
-      <c r="G23" s="107">
-        <v>0</v>
-      </c>
-      <c r="H23" s="99">
-        <v>0</v>
-      </c>
-      <c r="I23" s="100">
+      <c r="F23" s="101">
+        <v>0</v>
+      </c>
+      <c r="G23" s="101">
+        <v>0</v>
+      </c>
+      <c r="H23" s="93">
+        <v>0</v>
+      </c>
+      <c r="I23" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="102">
+      <c r="K23" s="96">
         <f>K8*E23%</f>
-        <v>5350.4236455930013</v>
-      </c>
-      <c r="L23" s="102"/>
-      <c r="M23" s="103">
+        <v>3981.1725285930011</v>
+      </c>
+      <c r="L23" s="96"/>
+      <c r="M23" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N23" s="104">
+      <c r="N23" s="98">
         <f t="shared" si="3"/>
-        <v>5350.4236455930013</v>
+        <v>3981.1725285930011</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2199,7 +2206,7 @@
       </c>
       <c r="K24" s="67">
         <f>K8*E24%</f>
-        <v>4847.3923626740016</v>
+        <v>3606.8742566740016</v>
       </c>
       <c r="L24" s="67"/>
       <c r="M24" s="68">
@@ -2208,54 +2215,54 @@
       </c>
       <c r="N24" s="84">
         <f t="shared" si="3"/>
-        <v>4847.3923626740016</v>
+        <v>3606.8742566740016</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>17</v>
       </c>
-      <c r="B25" s="105">
+      <c r="B25" s="99">
         <v>17</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="108" t="s">
+      <c r="D25" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="96">
+      <c r="E25" s="90">
         <v>0.51</v>
       </c>
-      <c r="F25" s="107">
-        <v>0</v>
-      </c>
-      <c r="G25" s="107">
-        <v>0</v>
-      </c>
-      <c r="H25" s="99">
-        <v>0</v>
-      </c>
-      <c r="I25" s="100">
+      <c r="F25" s="101">
+        <v>0</v>
+      </c>
+      <c r="G25" s="101">
+        <v>0</v>
+      </c>
+      <c r="H25" s="93">
+        <v>0</v>
+      </c>
+      <c r="I25" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="102">
+      <c r="K25" s="96">
         <f>K8*E25%</f>
-        <v>2332.235948079001</v>
-      </c>
-      <c r="L25" s="102"/>
-      <c r="M25" s="109">
+        <v>1735.3828970790007</v>
+      </c>
+      <c r="L25" s="96"/>
+      <c r="M25" s="103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N25" s="104">
+      <c r="N25" s="98">
         <f t="shared" si="3"/>
-        <v>2332.235948079001</v>
+        <v>1735.3828970790007</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2293,7 +2300,7 @@
       </c>
       <c r="K26" s="45">
         <f>K8*E26%</f>
-        <v>1234.7131489830003</v>
+        <v>918.73212198300041</v>
       </c>
       <c r="L26" s="45"/>
       <c r="M26" s="43">
@@ -2302,7 +2309,7 @@
       </c>
       <c r="N26" s="85">
         <f t="shared" si="3"/>
-        <v>1234.7131489830003</v>
+        <v>918.73212198300041</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,7 +2347,7 @@
       </c>
       <c r="K27" s="45">
         <f>K8*E27%</f>
-        <v>8322.8812264780026</v>
+        <v>6192.935044478003</v>
       </c>
       <c r="L27" s="45"/>
       <c r="M27" s="43">
@@ -2349,7 +2356,7 @@
       </c>
       <c r="N27" s="85">
         <f t="shared" si="3"/>
-        <v>8322.8812264780026</v>
+        <v>6192.935044478003</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2525,7 +2532,7 @@
       </c>
       <c r="K32" s="45">
         <f>K27+K26+K25+K24+K23+K22+K21+K20+K18+K19+K17+K16+K15+K14+K13+K12+K11+K10</f>
-        <v>457301.16629000014</v>
+        <v>340271.15629000013</v>
       </c>
       <c r="L32" s="45">
         <f>SUM(L10:L31)</f>
@@ -2537,7 +2544,7 @@
       </c>
       <c r="N32" s="19">
         <f>N27+N26+N25+N24+N23+N22+N21+N20+N19+N18+N17+N16+N15+N14+N13++N12+N11+N10</f>
-        <v>748259.39</v>
+        <v>631229.37999999989</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2567,7 +2574,7 @@
       </c>
       <c r="N33" s="29">
         <f>SUM(N10:N32)</f>
-        <v>1496518.7800000003</v>
+        <v>1262458.7599999998</v>
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="2" t="e">
@@ -2579,20 +2586,20 @@
       <c r="A34" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="106"/>
       <c r="O34" s="31"/>
       <c r="P34" s="2" t="e">
         <f t="shared" si="4"/>
@@ -2608,61 +2615,61 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="110" t="s">
+      <c r="C36" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="110"/>
-      <c r="E36" s="110"/>
-      <c r="F36" s="110"/>
-      <c r="G36" s="110"/>
-      <c r="H36" s="110"/>
-      <c r="I36" s="110"/>
-      <c r="J36" s="110"/>
-      <c r="K36" s="110"/>
-      <c r="L36" s="110"/>
-      <c r="M36" s="110"/>
+      <c r="D36" s="109"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="109"/>
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="110"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="110"/>
-      <c r="F37" s="110"/>
-      <c r="G37" s="110"/>
-      <c r="H37" s="110"/>
-      <c r="I37" s="110"/>
-      <c r="J37" s="110"/>
-      <c r="K37" s="110"/>
-      <c r="L37" s="110"/>
-      <c r="M37" s="110"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="109"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="109"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="109"/>
       <c r="P37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
-      <c r="J38" s="110"/>
-      <c r="K38" s="110"/>
-      <c r="L38" s="110"/>
-      <c r="M38" s="110"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="109"/>
       <c r="P38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="110"/>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="110"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="110"/>
-      <c r="L39" s="110"/>
-      <c r="M39" s="110"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="109"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109"/>
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
       <c r="P39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6542,21 +6549,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="91"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="107"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8148,19 +8155,19 @@
       <c r="A35" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="92" t="s">
+      <c r="C35" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="90"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="106"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
